--- a/data/trans_camb/IP1004-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1004-Estudios-trans_camb.xlsx
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 1,84</t>
+          <t>-4,62; 2,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,41; -0,77</t>
+          <t>-5,59; -0,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 0,98</t>
+          <t>-2,3; 0,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 0,0</t>
+          <t>-3,1; -0,37</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,0</t>
+          <t>-0,88; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,63</t>
+          <t>-0,39; 0,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,33</t>
+          <t>-0,62; 0,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,0</t>
+          <t>-0,77; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,1</t>
+          <t>-0,51; 0,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,2</t>
+          <t>-0,46; 0,2</t>
         </is>
       </c>
     </row>
@@ -943,17 +943,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,89</t>
+          <t>-0,79; 1,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 0,0</t>
+          <t>-2,33; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 2,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1,39</t>
+          <t>-0,38; 1,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,33</t>
+          <t>-0,51; 0,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,38</t>
+          <t>-0,42; 0,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,43</t>
+          <t>-0,61; 0,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; -0,18</t>
+          <t>-0,93; -0,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,21</t>
+          <t>-0,46; 0,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; -0,0</t>
+          <t>-0,59; -0,01</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 350,5</t>
+          <t>-90,79; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-87,69; 158,54</t>
+          <t>-87,77; 157,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 37,97</t>
+          <t>-100,0; 52,41</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1004-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1004-Estudios-trans_camb.xlsx
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 2,21</t>
+          <t>-4,62; 1,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,59; -0,76</t>
+          <t>-6,24; -0,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,83</t>
+          <t>-2,23; 1,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,1; -0,37</t>
+          <t>-3,08; -0,37</t>
         </is>
       </c>
     </row>
@@ -792,27 +792,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,71</t>
+          <t>-0,41; 0,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,33</t>
+          <t>-0,51; 0,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,0</t>
+          <t>-0,88; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,09</t>
+          <t>-0,5; 0,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,2</t>
+          <t>-0,43; 0,2</t>
         </is>
       </c>
     </row>
@@ -943,17 +943,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,98</t>
+          <t>-1,02; 1,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,0</t>
+          <t>-1,96; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,12</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 1,4</t>
+          <t>-0,41; 1,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,0</t>
+          <t>-1,18; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,23</t>
+          <t>-0,52; 0,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,39</t>
+          <t>-0,42; 0,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 0,46</t>
+          <t>-0,62; 0,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; -0,1</t>
+          <t>-1,01; -0,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,2</t>
+          <t>-0,45; 0,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,59; -0,01</t>
+          <t>-0,57; -0,0</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-90,79; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-87,77; 157,41</t>
+          <t>-86,23; 217,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 52,41</t>
+          <t>-100,0; 97,24</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1004-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1004-Estudios-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-2,35</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,33</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-2,35</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,24; 1,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,41; -0,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 1,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,24; -0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,08</t>
+          <t>-2,27; 0,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,08; -0,37</t>
+          <t>-2,72; 0,0</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-56,39%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-56,39%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,25</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-0,18</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,11</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,25</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,0</t>
+          <t>-0,57; 0,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,54</t>
+          <t>-0,89; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,35</t>
+          <t>-0,99; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,0</t>
+          <t>-0,53; 0,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,15</t>
+          <t>-0,47; 0,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 0,2</t>
+          <t>-0,42; 0,2</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-40,47%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>63,76%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-40,47%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,45</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,09</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-0,39</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,45</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,5</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,71</t>
+          <t>-0,79; 1,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,99; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,17</t>
+          <t>-0,21; 1,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 0,0</t>
+          <t>-1,03; 0,0</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>21,76%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-0,1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-0,01</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,23</t>
+          <t>-0,63; 0,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,37</t>
+          <t>-0,99; -0,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,46</t>
+          <t>-0,42; 0,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; -0,18</t>
+          <t>-0,42; 0,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,19</t>
+          <t>-0,44; 0,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; -0,0</t>
+          <t>-0,55; -0,0</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-29,41%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-46,2%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-7,07%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-29,41%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 350,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-86,23; 217,77</t>
+          <t>-87,69; 158,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 97,24</t>
+          <t>-100,0; 37,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1004-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1004-Estudios-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -118,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -131,6 +134,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -591,467 +600,259 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-1,33</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-2,35</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,66</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-1,15</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-1.327195124315111</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-2.353633090101663</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-0.6613937361567594</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-1.150178253558232</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-5,24; 1,84</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-6,41; -0,77</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-2,27; 0,98</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-2,72; 0,0</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-5.240002826722635</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-6.406016492333831</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="n">
+        <v>-2.268674670200758</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-2.721705404540589</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-56,39%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-57,5%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.84171265581653</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>-0.7704461120456099</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="n">
+        <v>0.9820254651137743</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>-0.5638921078636706</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="n">
+        <v>-0.5750358556255506</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,25</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,18</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-0,08</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-0,57; 0,33</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-0,89; 0,0</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-0,99; 0,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-0,53; 0,63</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-0,47; 0,1</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-0,42; 0,2</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-40,47%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>63,76%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-63,68%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-34,95%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>-0.1027954317292932</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.2539854488905428</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.1758794977391338</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.112135692978201</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-0.1385740793927856</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-0.07605231578650061</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.5673389089365923</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.8895391663703525</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-0.9850034690962335</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-0.5256456212117956</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-0.4712279367215953</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.4217828709347822</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,45</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,09</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,39</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,26</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-0,21</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.3269722179762096</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.6333812923257892</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.1033744123779075</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.2008235229407869</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,1</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,79; 1,89</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-1,99; 0,0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-0,21; 1,39</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-1,03; 0,0</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>-0.4047296102131968</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.6375711462658473</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.6368420437735909</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.3495120619340814</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>21,76%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>126,23%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1059,153 +860,277 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,01</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,11</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-0,24</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>0.4531865005860073</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.08541233005330767</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.3925849975539448</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.2596588052896472</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-0.2057040415579985</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-0,63; 0,43</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-0,99; -0,18</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-0,42; 0,33</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-0,42; 0,38</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-0,44; 0,21</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-0,55; -0,0</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="n">
+        <v>-0.787632441604067</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.989216976999446</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-0.2063503052837315</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-1.031214584050288</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>-29,41%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-46,2%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-7,07%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-34,54%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-71,81%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.09539027282717</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="n">
+        <v>1.894177185420592</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>1.393321629947694</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 350,5</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-87,69; 158,54</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 37,97</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr"/>
+      <c r="E19" s="6" t="n">
+        <v>0.2175639175859521</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>1.262293163143496</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.1326003022277636</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.4509151407189051</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.096004890423765</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.01468338237896115</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-0.1149702444493392</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-0.2390440863601432</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.6317333546108796</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.9913673756861722</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.4177342636904079</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-0.4225927003426748</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-0.4447616740088908</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-0.5465679518608088</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.4341328732706985</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>-0.1759950362376045</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.3332035787343789</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.3843186445652686</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.2114400562916677</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>-0.0001861467962111081</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>-0.2940693054049055</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.4620031643587105</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.07066066210403935</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.3453530331136057</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.7180518808823024</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="n">
+        <v>-0.8768865232785077</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>3.505009214392971</v>
+      </c>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="n">
+        <v>1.58540884539791</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.3796512161615254</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1213,14 +1138,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A4:A9"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
